--- a/data/df_ref.xlsx
+++ b/data/df_ref.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="263" documentId="8_{0DF2F44A-0C0C-4158-B4BC-0F2F8222436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E32E3E5-00C8-4A9E-956B-B9324A8AA817}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD2A8B5B-42C3-4201-A900-B2422E17A3CB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD2A8B5B-42C3-4201-A900-B2422E17A3CB}"/>
   </bookViews>
   <sheets>
     <sheet name="df_ref" sheetId="1" r:id="rId1"/>

--- a/data/df_ref.xlsx
+++ b/data/df_ref.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hersheys-my.sharepoint.com/personal/dsmithds_hersheys_com/Documents/misc/lebanon_ctc/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="263" documentId="8_{0DF2F44A-0C0C-4158-B4BC-0F2F8222436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E32E3E5-00C8-4A9E-956B-B9324A8AA817}"/>
+  <xr:revisionPtr revIDLastSave="300" documentId="8_{0DF2F44A-0C0C-4158-B4BC-0F2F8222436A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD243CCE-06F5-44B3-A167-60FB61C8907E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD2A8B5B-42C3-4201-A900-B2422E17A3CB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD2A8B5B-42C3-4201-A900-B2422E17A3CB}"/>
   </bookViews>
   <sheets>
     <sheet name="df_ref" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">df_ref!$A$1:$F$241</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="559">
   <si>
     <t>category</t>
   </si>
@@ -1694,6 +1697,9 @@
   </si>
   <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>Info</t>
   </si>
 </sst>
 </file>
@@ -3330,8 +3336,8 @@
       <c r="E38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>557</v>
+      <c r="F38" s="4" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3551,7 +3557,7 @@
         <v>127</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3571,7 +3577,7 @@
         <v>129</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3591,7 +3597,7 @@
         <v>130</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3611,7 +3617,7 @@
         <v>131</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3631,7 +3637,7 @@
         <v>132</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3651,7 +3657,7 @@
         <v>133</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3671,7 +3677,7 @@
         <v>134</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3691,7 +3697,7 @@
         <v>139</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3711,7 +3717,7 @@
         <v>141</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3731,7 +3737,7 @@
         <v>143</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3751,7 +3757,7 @@
         <v>145</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3771,7 +3777,7 @@
         <v>147</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3791,7 +3797,7 @@
         <v>149</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -3811,7 +3817,7 @@
         <v>151</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
@@ -4131,7 +4137,7 @@
         <v>189</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4190,8 +4196,8 @@
       <c r="E81" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>556</v>
+      <c r="F81" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -4210,8 +4216,8 @@
       <c r="E82" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>556</v>
+      <c r="F82" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4230,8 +4236,8 @@
       <c r="E83" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>556</v>
+      <c r="F83" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="84" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4250,8 +4256,8 @@
       <c r="E84" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>556</v>
+      <c r="F84" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="85" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4270,8 +4276,8 @@
       <c r="E85" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>556</v>
+      <c r="F85" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="86" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4290,8 +4296,8 @@
       <c r="E86" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>556</v>
+      <c r="F86" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="87" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -4310,8 +4316,8 @@
       <c r="E87" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>556</v>
+      <c r="F87" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="88" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -4330,8 +4336,8 @@
       <c r="E88" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>556</v>
+      <c r="F88" s="4" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4811,7 +4817,7 @@
         <v>269</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="113" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4831,7 +4837,7 @@
         <v>271</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="114" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4851,7 +4857,7 @@
         <v>273</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="115" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4871,7 +4877,7 @@
         <v>275</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="116" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4891,7 +4897,7 @@
         <v>277</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4911,7 +4917,7 @@
         <v>279</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="118" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4931,7 +4937,7 @@
         <v>281</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4951,7 +4957,7 @@
         <v>283</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4971,7 +4977,7 @@
         <v>285</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -4991,7 +4997,7 @@
         <v>287</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5011,7 +5017,7 @@
         <v>289</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5031,7 +5037,7 @@
         <v>291</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5051,7 +5057,7 @@
         <v>293</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="125" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5071,7 +5077,7 @@
         <v>295</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="126" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5091,7 +5097,7 @@
         <v>297</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="127" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -5111,7 +5117,7 @@
         <v>299</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="128" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -6591,7 +6597,7 @@
         <v>462</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6611,7 +6617,7 @@
         <v>464</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6631,7 +6637,7 @@
         <v>466</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6651,7 +6657,7 @@
         <v>468</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6671,7 +6677,7 @@
         <v>470</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -6691,7 +6697,7 @@
         <v>472</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7191,7 +7197,7 @@
         <v>530</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7211,7 +7217,7 @@
         <v>532</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7231,7 +7237,7 @@
         <v>534</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7251,7 +7257,7 @@
         <v>536</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
@@ -7271,7 +7277,7 @@
         <v>538</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -7395,6 +7401,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F241" xr:uid="{F7F637D7-4BF5-4783-AFE2-2BFE8F07EAAA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
